--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1086,25 +1086,47 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>840</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>I don’t like to stay here</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1130,25 +1133,47 @@
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>200</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1149,21 +1149,21 @@
         <v>120</v>
       </c>
       <c r="F9" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G9" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H9" s="14">
         <v>0</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>740</v>
+        <v>840</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>57</v>
@@ -1177,25 +1177,47 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B10" s="14">
+        <v>450</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>180</v>
+      </c>
+      <c r="F10" s="14">
+        <v>350</v>
+      </c>
+      <c r="G10" s="14">
+        <v>350</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">

--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1221,25 +1221,47 @@
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B11" s="14">
+        <v>310</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>240</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1265,25 +1268,47 @@
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B12" s="14">
+        <v>120</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>150</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+        <v>950</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">

--- a/12602406.xlsx
+++ b/12602406.xlsx
@@ -1155,7 +1155,7 @@
         <v>300</v>
       </c>
       <c r="G9" s="14">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="H9" s="14">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>350</v>
       </c>
       <c r="G10" s="14">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="H10" s="14">
         <v>0</v>
@@ -1243,7 +1243,7 @@
         <v>300</v>
       </c>
       <c r="G11" s="14">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="H11" s="14">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>250</v>
       </c>
       <c r="G12" s="14">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="H12" s="14">
         <v>0</v>
